--- a/automation-agency/templates/leads-plumbers-oct-2026.xlsx
+++ b/automation-agency/templates/leads-plumbers-oct-2026.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:N162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -519,7 +519,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>20 אינסטלטורים לפנייה</t>
+          <t>150 אינסטלטורים לפנייה, מכל הארץ</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
           <t>אינסטלציה אונו</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr"/>
+      <c r="C9" s="4" t="n"/>
       <c r="D9" s="4" t="inlineStr">
         <is>
           <t>קריית אונו, גבעת שמואל, סביון</t>
@@ -1169,7 +1169,7 @@
           <t>ענקי אינסטלציה</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr"/>
+      <c r="C15" s="4" t="n"/>
       <c r="D15" s="4" t="inlineStr">
         <is>
           <t>רחובות</t>
@@ -1221,7 +1221,7 @@
           <t>אדיר אינסטלציה</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr"/>
+      <c r="C16" s="4" t="n"/>
       <c r="D16" s="4" t="inlineStr">
         <is>
           <t>ירושלים</t>
@@ -1232,7 +1232,7 @@
           <t>052-3303060</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="n"/>
       <c r="G16" s="4" t="inlineStr">
         <is>
           <t>6 ביקורות, 4.4</t>
@@ -1269,7 +1269,7 @@
           <t>אביר שרותי אינסטלציה</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr"/>
+      <c r="C17" s="4" t="n"/>
       <c r="D17" s="4" t="inlineStr">
         <is>
           <t>ראשל"צ, חולון, ת"א, פ"ת, רחובות</t>
@@ -1377,7 +1377,7 @@
           <t>א.א.א. אחים בן חמו</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr"/>
+      <c r="C19" s="4" t="n"/>
       <c r="D19" s="4" t="inlineStr">
         <is>
           <t>פתח תקווה</t>
@@ -1388,7 +1388,7 @@
           <t>050-5292488</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="n"/>
       <c r="G19" s="4" t="inlineStr">
         <is>
           <t>1 ביקורת, 5.0</t>
@@ -1415,44 +1415,44 @@
       <c r="N19" s="7" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>ב</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>הצוות - אינסטלציה ומשאבות</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr"/>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>יהוד-מונוסון</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>052-3391530</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr"/>
-      <c r="G20" s="8" t="inlineStr">
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>אין ביקורות</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>24 שעות ביממה, גם משאבות</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>ראיתי שאתם עובדים 24 שעות ביממה. כשכולם בשטח ומתקשרים, מי עונה?</t>
         </is>
       </c>
-      <c r="J20" s="10" t="inlineStr">
+      <c r="J20" s="6" t="inlineStr">
         <is>
           <t>דף העסק</t>
         </is>
@@ -1463,44 +1463,44 @@
       <c r="N20" s="7" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>ב</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>אופק אינסטלציה</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr"/>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>ירושלים</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>052-6802020</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr"/>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>אין דירוג (b144)</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>מפרסם 'אינסטלטור 24 שעות'. אולי עסק גדול</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>ראיתי שאתה מפרסם אינסטלטור 24 שעות. כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
         </is>
       </c>
-      <c r="J21" s="10" t="inlineStr">
+      <c r="J21" s="6" t="inlineStr">
         <is>
           <t>דף העסק</t>
         </is>
@@ -1511,48 +1511,48 @@
       <c r="N21" s="7" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>ב</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>ליעד שירותי אינסטלציה</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>ליעד</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>ירושלים, עמק רפאים</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>054-7907716</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr"/>
-      <c r="G22" s="8" t="inlineStr">
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>אין ביקורות</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>24 שעות א'-ה', שירות גם באנגלית</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>ראיתי שאתה עובד 24 שעות ונותן שירות גם באנגלית. כשאתה באמצע עבודה ומתקשרים, מה קורה?</t>
         </is>
       </c>
-      <c r="J22" s="10" t="inlineStr">
+      <c r="J22" s="6" t="inlineStr">
         <is>
           <t>דף העסק</t>
         </is>
@@ -1563,48 +1563,48 @@
       <c r="N22" s="7" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>ב</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>אינסטלציה יניב</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>יניב</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>ירושלים, פסגת זאב</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>050-2118987</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr"/>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>אין ביקורות</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>עסק שכונתי, א'-ה' 7:30-19:30</t>
         </is>
       </c>
-      <c r="I23" s="8" t="inlineStr">
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>ראיתי שאתה האינסטלטור של פסגת זאב. כשמתקשרים אחרי 19:30 או באמצע עבודה, מה קורה עם השיחה?</t>
         </is>
       </c>
-      <c r="J23" s="10" t="inlineStr">
+      <c r="J23" s="6" t="inlineStr">
         <is>
           <t>דף העסק</t>
         </is>
@@ -1615,48 +1615,48 @@
       <c r="N23" s="7" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>ב</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>חזי חיים אינסטלציה והסקות</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>חזי</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>מבשרת ציון</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>050-2673111</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr"/>
-      <c r="G24" s="8" t="inlineStr">
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>אין ביקורות</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>אינסטלציה וגם הסקה</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>ראיתי שאתה עושה גם הסקה, אז בחורף זה בטח מתפוצץ. כשאתה באמצע עבודה ומתקשרים, מה קורה?</t>
         </is>
       </c>
-      <c r="J24" s="10" t="inlineStr">
+      <c r="J24" s="6" t="inlineStr">
         <is>
           <t>דף העסק</t>
         </is>
@@ -1666,45 +1666,5765 @@
       <c r="M24" s="7" t="n"/>
       <c r="N24" s="7" t="n"/>
     </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>א</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>אבי את אבי אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>גני תקווה</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>054-6044406</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>28 ביקורות, 4.5</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="n"/>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>יש לך 28 ביקורות, עובדים איתך הרבה. כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/15164260/2550/</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="n"/>
+      <c r="L25" s="7" t="n"/>
+      <c r="M25" s="7" t="n"/>
+      <c r="N25" s="7" t="n"/>
+    </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>א</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>גלבינסקי דניאל</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>כרמיאל</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>052-2361983</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>33 ביקורות, 4.8</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="n"/>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>יש לך 33 ביקורות, עובדים איתך הרבה. כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/639090/2550/</t>
+        </is>
+      </c>
+      <c r="K26" s="7" t="n"/>
+      <c r="L26" s="7" t="n"/>
+      <c r="M26" s="7" t="n"/>
+      <c r="N26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>א</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>אינסטלטוב</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>חיפה</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>052-2982782</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>11 ביקורות, 4.7</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>יש לך 11 ביקורות, עובדים איתך הרבה. כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80058714/2550/</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="n"/>
+      <c r="L27" s="7" t="n"/>
+      <c r="M27" s="7" t="n"/>
+      <c r="N27" s="7" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>א</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>יצחק קלדרון אינסטלציה בע"מ</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>נשר</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>050-5263250</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>24 ביקורות, 4.3</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>יש לך 24 ביקורות, עובדים איתך הרבה. כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/29808940/2550/</t>
+        </is>
+      </c>
+      <c r="K28" s="7" t="n"/>
+      <c r="L28" s="7" t="n"/>
+      <c r="M28" s="7" t="n"/>
+      <c r="N28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>א</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>אורי אינסטלטור מוסמך 24/7</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>קרית מוצקין</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>054-4645174</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>7 ביקורות, 5.0</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="n"/>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80260336/2550/</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="n"/>
+      <c r="L29" s="7" t="n"/>
+      <c r="M29" s="7" t="n"/>
+      <c r="N29" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>א</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>האינסטלטור חיים שטח</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>חיפה</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>052-8527930</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>5 ביקורות, 4.9</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="n"/>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80116139/2550/</t>
+        </is>
+      </c>
+      <c r="K30" s="7" t="n"/>
+      <c r="L30" s="7" t="n"/>
+      <c r="M30" s="7" t="n"/>
+      <c r="N30" s="7" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>א</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>אורפז - לוי ניסים</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>כרמיאל</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>050-5368865</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>19 ביקורות, 4.6</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>יש לך 19 ביקורות, עובדים איתך הרבה. כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/28331760/2550/</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="n"/>
+      <c r="L31" s="7" t="n"/>
+      <c r="M31" s="7" t="n"/>
+      <c r="N31" s="7" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>א</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>טכנולוגיות העמקים</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>קרית טבעון</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>054-9874545</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>2 ביקורות, 5.0</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="n"/>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80391211/2550/</t>
+        </is>
+      </c>
+      <c r="K32" s="7" t="n"/>
+      <c r="L32" s="7" t="n"/>
+      <c r="M32" s="7" t="n"/>
+      <c r="N32" s="7" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>א</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>מקס המאתר איתור נזילות</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>קרית אתא</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>054-4418816</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>2 ביקורות, 4.8</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/37584550/2550/</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="n"/>
+      <c r="L33" s="7" t="n"/>
+      <c r="M33" s="7" t="n"/>
+      <c r="N33" s="7" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>א</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>גואטה שירותי אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>נהריה</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>052-5402288</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>13 ביקורות, 4.9</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="n"/>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>יש לך 13 ביקורות, עובדים איתך הרבה. כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/21732350/2550/</t>
+        </is>
+      </c>
+      <c r="K34" s="7" t="n"/>
+      <c r="L34" s="7" t="n"/>
+      <c r="M34" s="7" t="n"/>
+      <c r="N34" s="7" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>א</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>sunrise דודי שמש ועבודות אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>כרמיאל</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>050-4916380</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="n"/>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>1 ביקורת, 5.0</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="n"/>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>אתה מפרסם בדפי זהב, משלם שיתקשרו. כמה שיחות נופלות כשאתה באמצע עבודה?</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80346284/2550/</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="n"/>
+      <c r="L35" s="7" t="n"/>
+      <c r="M35" s="7" t="n"/>
+      <c r="N35" s="7" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>א</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>מישל אינסטלציה ושיפוצים</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>נתניה</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>050-7201280</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>1 ביקורת, 5.0</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="n"/>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>אתה מפרסם בדפי זהב, משלם שיתקשרו. כמה שיחות נופלות כשאתה באמצע עבודה?</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80170966/2550/</t>
+        </is>
+      </c>
+      <c r="K36" s="7" t="n"/>
+      <c r="L36" s="7" t="n"/>
+      <c r="M36" s="7" t="n"/>
+      <c r="N36" s="7" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>א</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>לירון אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>רעננה</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>050-4227889</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>10 ביקורות, 4.4</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="n"/>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>יש לך 10 ביקורות, עובדים איתך הרבה. כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80046135/2550/</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="n"/>
+      <c r="L37" s="7" t="n"/>
+      <c r="M37" s="7" t="n"/>
+      <c r="N37" s="7" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>א</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>בורה שרותי ביוב ואינסטלציה בע"מ</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>זכרון יעקב</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>050-7100909</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>53 ביקורות, 4.7</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="n"/>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>יש לך 53 ביקורות, עובדים איתך הרבה. כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80170571/2550/</t>
+        </is>
+      </c>
+      <c r="K38" s="7" t="n"/>
+      <c r="L38" s="7" t="n"/>
+      <c r="M38" s="7" t="n"/>
+      <c r="N38" s="7" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>א</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>חסין יהודה-אינסטלציה ושיפוצים</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>טבריה</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>050-5279320</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>31 ביקורות, 4.7</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="n"/>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>יש לך 31 ביקורות, עובדים איתך הרבה. כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/6561650/2550/</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="n"/>
+      <c r="L39" s="7" t="n"/>
+      <c r="M39" s="7" t="n"/>
+      <c r="N39" s="7" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>א</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>רחמני שאיבות</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>זכרון יעקב</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>050-5351287</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="n"/>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>18 ביקורות, 4.4</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>יש לך 18 ביקורות, עובדים איתך הרבה. כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/4788910/2550/</t>
+        </is>
+      </c>
+      <c r="K40" s="7" t="n"/>
+      <c r="L40" s="7" t="n"/>
+      <c r="M40" s="7" t="n"/>
+      <c r="N40" s="7" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>א</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>טוהר שירותי אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>קרית שמונה</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>054-6897797</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="n"/>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>13 ביקורות, 4.4</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="n"/>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>יש לך 13 ביקורות, עובדים איתך הרבה. כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80292122/2550/</t>
+        </is>
+      </c>
+      <c r="K41" s="7" t="n"/>
+      <c r="L41" s="7" t="n"/>
+      <c r="M41" s="7" t="n"/>
+      <c r="N41" s="7" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>א</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>עסק טוב-כהן יואב</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n"/>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>פרדס חנה-כרכור</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>050-5281381</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="n"/>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>6 ביקורות, 4.5</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="n"/>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/8623750/2550/</t>
+        </is>
+      </c>
+      <c r="K42" s="7" t="n"/>
+      <c r="L42" s="7" t="n"/>
+      <c r="M42" s="7" t="n"/>
+      <c r="N42" s="7" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>א</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>שואבי קצרין והגולן</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n"/>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>קצרין</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>052-4849198</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="n"/>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>5 ביקורות, 5.0</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="n"/>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80178734/2550/</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="n"/>
+      <c r="L43" s="7" t="n"/>
+      <c r="M43" s="7" t="n"/>
+      <c r="N43" s="7" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>א</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>רמי סעדון שירותי אינסטלציה בטכנולוגיה מתקדמת</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="n"/>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>עפולה</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>052-4281911</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="n"/>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>3 ביקורות, 5.0</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="n"/>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80287608/2550/</t>
+        </is>
+      </c>
+      <c r="K44" s="7" t="n"/>
+      <c r="L44" s="7" t="n"/>
+      <c r="M44" s="7" t="n"/>
+      <c r="N44" s="7" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>א</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>אטדגי ניסים מיצאת צדיק</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>אור עקיבא</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>050-2478241</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>6 ביקורות, 4.4</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="n"/>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>אתה מפרסם בדפי זהב, משלם שיתקשרו. כמה שיחות נופלות כשאתה באמצע עבודה?</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80129829/2550/</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="n"/>
+      <c r="L45" s="7" t="n"/>
+      <c r="M45" s="7" t="n"/>
+      <c r="N45" s="7" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>א</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>נשיא אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>צפת</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>050-2504929</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="n"/>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>2 ביקורות, 5.0</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="n"/>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80389167/2550/</t>
+        </is>
+      </c>
+      <c r="K46" s="7" t="n"/>
+      <c r="L46" s="7" t="n"/>
+      <c r="M46" s="7" t="n"/>
+      <c r="N46" s="7" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>א</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>שקד שירותי אינסטלציה וביוב</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="n"/>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>עפולה</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>054-9097951</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="n"/>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>6 ביקורות, 5.0</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="n"/>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80292057/2550/</t>
+        </is>
+      </c>
+      <c r="K47" s="7" t="n"/>
+      <c r="L47" s="7" t="n"/>
+      <c r="M47" s="7" t="n"/>
+      <c r="N47" s="7" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>א</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>קו מערכות צנרת</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="n"/>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>צפת</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>050-2605029</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="n"/>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>6 ביקורות, 5.0</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="n"/>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80317812/2550/</t>
+        </is>
+      </c>
+      <c r="K48" s="7" t="n"/>
+      <c r="L48" s="7" t="n"/>
+      <c r="M48" s="7" t="n"/>
+      <c r="N48" s="7" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>א</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>ירון אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="n"/>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>זכרון יעקב</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>054-2877314</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="n"/>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>5 ביקורות, 5.0</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="n"/>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80302397/2550/</t>
+        </is>
+      </c>
+      <c r="K49" s="7" t="n"/>
+      <c r="L49" s="7" t="n"/>
+      <c r="M49" s="7" t="n"/>
+      <c r="N49" s="7" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>א</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>דורון אינסטלציה ושיפוצים</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="n"/>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>באר שבע</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>052-2884224</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="n"/>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>39 ביקורות, 4.5</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="n"/>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>יש לך 39 ביקורות, עובדים איתך הרבה. כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80060730/2550/</t>
+        </is>
+      </c>
+      <c r="K50" s="7" t="n"/>
+      <c r="L50" s="7" t="n"/>
+      <c r="M50" s="7" t="n"/>
+      <c r="N50" s="7" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>א</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>חנן - חבל על כל טיפה</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n"/>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>אילת</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>052-3449018</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="n"/>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>25 ביקורות, 4.6</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="n"/>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>יש לך 25 ביקורות, עובדים איתך הרבה. כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/71677290/2550/</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="n"/>
+      <c r="L51" s="7" t="n"/>
+      <c r="M51" s="7" t="n"/>
+      <c r="N51" s="7" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>א</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>א.ת. שיפוצים</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>באר שבע</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>054-2668843</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="n"/>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>8 ביקורות, 5.0</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="n"/>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>אתה מפרסם בדפי זהב, משלם שיתקשרו. כמה שיחות נופלות כשאתה באמצע עבודה?</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80355889/2550/</t>
+        </is>
+      </c>
+      <c r="K52" s="7" t="n"/>
+      <c r="L52" s="7" t="n"/>
+      <c r="M52" s="7" t="n"/>
+      <c r="N52" s="7" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>א</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>י.ש אחזקות</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n"/>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>אילת</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>054-5401318</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="n"/>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>6 ביקורות, 4.3</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="n"/>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80222120/2550/</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="n"/>
+      <c r="L53" s="7" t="n"/>
+      <c r="M53" s="7" t="n"/>
+      <c r="N53" s="7" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>א</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>השרברבים בע"מ</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n"/>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>באר שבע</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>053-7741646</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="n"/>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>1 ביקורת, 4.8</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="n"/>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>אתה מפרסם בדפי זהב, משלם שיתקשרו. כמה שיחות נופלות כשאתה באמצע עבודה?</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/2560810/2550/</t>
+        </is>
+      </c>
+      <c r="K54" s="7" t="n"/>
+      <c r="L54" s="7" t="n"/>
+      <c r="M54" s="7" t="n"/>
+      <c r="N54" s="7" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>א</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>אינסטלטור עומר</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n"/>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>לוד</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>052-6661615</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="n"/>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>14 ביקורות, 4.0</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="n"/>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>יש לך 14 ביקורות, עובדים איתך הרבה. כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/24326640/2550/</t>
+        </is>
+      </c>
+      <c r="K55" s="7" t="n"/>
+      <c r="L55" s="7" t="n"/>
+      <c r="M55" s="7" t="n"/>
+      <c r="N55" s="7" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>א</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>ש.ע. שירותי אינסטלציה ודודי שמש</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="n"/>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>רחובות</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>052-2519205</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="n"/>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>18 ביקורות, 4.0</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="n"/>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>יש לך 18 ביקורות, עובדים איתך הרבה. כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/34502280/2550/</t>
+        </is>
+      </c>
+      <c r="K56" s="7" t="n"/>
+      <c r="L56" s="7" t="n"/>
+      <c r="M56" s="7" t="n"/>
+      <c r="N56" s="7" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>א</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>דוד שירותי אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="n"/>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>אשדוד</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>052-6613966</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="n"/>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>1 ביקורת, 5.0</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="n"/>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80372220/2550/</t>
+        </is>
+      </c>
+      <c r="K57" s="7" t="n"/>
+      <c r="L57" s="7" t="n"/>
+      <c r="M57" s="7" t="n"/>
+      <c r="N57" s="7" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>א</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>אינסטלטורים בכחול</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="n"/>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>רחובות</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>052-7916595</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="n"/>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>8 ביקורות, 4.7</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="n"/>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80340978/2550/</t>
+        </is>
+      </c>
+      <c r="K58" s="7" t="n"/>
+      <c r="L58" s="7" t="n"/>
+      <c r="M58" s="7" t="n"/>
+      <c r="N58" s="7" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>א</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>שירותי אינסטלציה מקצועיים בבית שמש - יס אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="n"/>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>בית שמש</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>050-7707149</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="n"/>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>4 ביקורות, 5.0</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="n"/>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80359593/2550/</t>
+        </is>
+      </c>
+      <c r="K59" s="7" t="n"/>
+      <c r="L59" s="7" t="n"/>
+      <c r="M59" s="7" t="n"/>
+      <c r="N59" s="7" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>א</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>תדהר אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="n"/>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>ירושלים</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>050-5275451</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="n"/>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>1 ביקורת, 5.0</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="n"/>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>אתה מפרסם בדפי זהב, משלם שיתקשרו. כמה שיחות נופלות כשאתה באמצע עבודה?</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/33690630/2550/</t>
+        </is>
+      </c>
+      <c r="K60" s="7" t="n"/>
+      <c r="L60" s="7" t="n"/>
+      <c r="M60" s="7" t="n"/>
+      <c r="N60" s="7" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>גיא אלון הנדימן ואינסטלציה</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="n"/>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>ראשון לציון</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>054-7000038</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="n"/>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="n"/>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80036830/2550/</t>
+        </is>
+      </c>
+      <c r="K61" s="7" t="n"/>
+      <c r="L61" s="7" t="n"/>
+      <c r="M61" s="7" t="n"/>
+      <c r="N61" s="7" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>ספיד שירותי אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="n"/>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>תל אביב</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>050-3093930</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="n"/>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>4 ביקורות, 5.0</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="n"/>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80282815/2550/</t>
+        </is>
+      </c>
+      <c r="K62" s="7" t="n"/>
+      <c r="L62" s="7" t="n"/>
+      <c r="M62" s="7" t="n"/>
+      <c r="N62" s="7" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>מאסטר פיקס אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="n"/>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>תל אביב</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>052-5325298</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="n"/>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="n"/>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>אתה מפרסם בדפי זהב, משלם שיתקשרו. כמה שיחות נופלות כשאתה באמצע עבודה?</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80347743/2550/</t>
+        </is>
+      </c>
+      <c r="K63" s="7" t="n"/>
+      <c r="L63" s="7" t="n"/>
+      <c r="M63" s="7" t="n"/>
+      <c r="N63" s="7" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>ישראל אינסטלטור</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="n"/>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>חולון</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>050-9933110</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="n"/>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="n"/>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>אתה מפרסם בדפי זהב, משלם שיתקשרו. כמה שיחות נופלות כשאתה באמצע עבודה?</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80383285/2550/</t>
+        </is>
+      </c>
+      <c r="K64" s="7" t="n"/>
+      <c r="L64" s="7" t="n"/>
+      <c r="M64" s="7" t="n"/>
+      <c r="N64" s="7" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>מקצוען באינסטלציה</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="n"/>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>ראשון לציון</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>054-3013012</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="n"/>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="n"/>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>אתה מפרסם בדפי זהב, משלם שיתקשרו. כמה שיחות נופלות כשאתה באמצע עבודה?</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80393080/2550/</t>
+        </is>
+      </c>
+      <c r="K65" s="7" t="n"/>
+      <c r="L65" s="7" t="n"/>
+      <c r="M65" s="7" t="n"/>
+      <c r="N65" s="7" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>ברקאי שירותי אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>רמת גן</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>054-5203204</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="n"/>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>1 ביקורת, 5.0</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="n"/>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J66" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80237945/2550/</t>
+        </is>
+      </c>
+      <c r="K66" s="7" t="n"/>
+      <c r="L66" s="7" t="n"/>
+      <c r="M66" s="7" t="n"/>
+      <c r="N66" s="7" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>קו מים ניר</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="n"/>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>תל אביב</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>052-3547744</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="n"/>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>2 ביקורות, 5.0</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="n"/>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/63219390/2550/</t>
+        </is>
+      </c>
+      <c r="K67" s="7" t="n"/>
+      <c r="L67" s="7" t="n"/>
+      <c r="M67" s="7" t="n"/>
+      <c r="N67" s="7" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>דורון אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="n"/>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>בת ים</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>052-7916132</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="n"/>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>1 ביקורת, 5.0</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="n"/>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80107610/2550/</t>
+        </is>
+      </c>
+      <c r="K68" s="7" t="n"/>
+      <c r="L68" s="7" t="n"/>
+      <c r="M68" s="7" t="n"/>
+      <c r="N68" s="7" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>איתן שיפוצים</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="n"/>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>תל אביב</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>053-7374363</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="n"/>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>1 ביקורת, 5.0</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="n"/>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80040164/2550/</t>
+        </is>
+      </c>
+      <c r="K69" s="7" t="n"/>
+      <c r="L69" s="7" t="n"/>
+      <c r="M69" s="7" t="n"/>
+      <c r="N69" s="7" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>בוכניק דני</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="n"/>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>רמת גן</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>050-5365736</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="n"/>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>1 ביקורת, 5.0</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="n"/>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J70" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/38011490/2550/</t>
+        </is>
+      </c>
+      <c r="K70" s="7" t="n"/>
+      <c r="L70" s="7" t="n"/>
+      <c r="M70" s="7" t="n"/>
+      <c r="N70" s="7" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>אינפרא סורג'ון</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="n"/>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>חיפה</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>052-7507505</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="n"/>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="n"/>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/65647100/2550/</t>
+        </is>
+      </c>
+      <c r="K71" s="7" t="n"/>
+      <c r="L71" s="7" t="n"/>
+      <c r="M71" s="7" t="n"/>
+      <c r="N71" s="7" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>א. גולן מוקד תיקונים</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="n"/>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>חיפה</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>052-2690036</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="n"/>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="n"/>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J72" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80372599/2550/</t>
+        </is>
+      </c>
+      <c r="K72" s="7" t="n"/>
+      <c r="L72" s="7" t="n"/>
+      <c r="M72" s="7" t="n"/>
+      <c r="N72" s="7" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>אבי אמינות - מוקד אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="n"/>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>רמת ישי</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>052-5323118</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="n"/>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>4 ביקורות, 5.0</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="n"/>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J73" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/76714640/2550/</t>
+        </is>
+      </c>
+      <c r="K73" s="7" t="n"/>
+      <c r="L73" s="7" t="n"/>
+      <c r="M73" s="7" t="n"/>
+      <c r="N73" s="7" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>סימון מטרי עבודות אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="n"/>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>חיפה</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>054-9796382</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="n"/>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>3 ביקורות, 5.0</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="n"/>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J74" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80278693/2550/</t>
+        </is>
+      </c>
+      <c r="K74" s="7" t="n"/>
+      <c r="L74" s="7" t="n"/>
+      <c r="M74" s="7" t="n"/>
+      <c r="N74" s="7" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>בורטמן - ביובית ופתיחת סתימות</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="n"/>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>חיפה</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>052-4742050</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="n"/>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="n"/>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>אתה מפרסם בדפי זהב, משלם שיתקשרו. כמה שיחות נופלות כשאתה באמצע עבודה?</t>
+        </is>
+      </c>
+      <c r="J75" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80391196/2550/</t>
+        </is>
+      </c>
+      <c r="K75" s="7" t="n"/>
+      <c r="L75" s="7" t="n"/>
+      <c r="M75" s="7" t="n"/>
+      <c r="N75" s="7" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>כרמל עבודות אחזקה</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="n"/>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>חיפה</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>052-3956895</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="n"/>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>2 ביקורות, 5.0</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="n"/>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80176304/2550/</t>
+        </is>
+      </c>
+      <c r="K76" s="7" t="n"/>
+      <c r="L76" s="7" t="n"/>
+      <c r="M76" s="7" t="n"/>
+      <c r="N76" s="7" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>מורן שירותי אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="n"/>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>חיפה</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>055-6622252</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="n"/>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>1 ביקורת, 5.0</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="n"/>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J77" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80351072/2550/</t>
+        </is>
+      </c>
+      <c r="K77" s="7" t="n"/>
+      <c r="L77" s="7" t="n"/>
+      <c r="M77" s="7" t="n"/>
+      <c r="N77" s="7" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>דני מזור אינסטלטור</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="n"/>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>נהריה</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>050-3081000</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="n"/>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>3 ביקורות, 3.6</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="n"/>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J78" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80189287/2550/</t>
+        </is>
+      </c>
+      <c r="K78" s="7" t="n"/>
+      <c r="L78" s="7" t="n"/>
+      <c r="M78" s="7" t="n"/>
+      <c r="N78" s="7" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>שרברב הקריה</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="n"/>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>קרית אתא</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>050-5348246</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="n"/>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>2 ביקורות, 3.5</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="n"/>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J79" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/20041170/2550/</t>
+        </is>
+      </c>
+      <c r="K79" s="7" t="n"/>
+      <c r="L79" s="7" t="n"/>
+      <c r="M79" s="7" t="n"/>
+      <c r="N79" s="7" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>לוי אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="n"/>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>רשפון</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>050-5414514</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="n"/>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>3 ביקורות, 5.0</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="n"/>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J80" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80197810/2550/</t>
+        </is>
+      </c>
+      <c r="K80" s="7" t="n"/>
+      <c r="L80" s="7" t="n"/>
+      <c r="M80" s="7" t="n"/>
+      <c r="N80" s="7" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>ש.נ שרותי אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="n"/>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>בני ציון</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>050-9313882</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="n"/>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="n"/>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>אתה מפרסם בדפי זהב, משלם שיתקשרו. כמה שיחות נופלות כשאתה באמצע עבודה?</t>
+        </is>
+      </c>
+      <c r="J81" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80377174/2550/</t>
+        </is>
+      </c>
+      <c r="K81" s="7" t="n"/>
+      <c r="L81" s="7" t="n"/>
+      <c r="M81" s="7" t="n"/>
+      <c r="N81" s="7" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>שירי אחזקה שיפוצים ואינסטלציה</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="n"/>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>הוד השרון</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>050-5556800</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="n"/>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="n"/>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>אתה מפרסם בדפי זהב, משלם שיתקשרו. כמה שיחות נופלות כשאתה באמצע עבודה?</t>
+        </is>
+      </c>
+      <c r="J82" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80383508/2550/</t>
+        </is>
+      </c>
+      <c r="K82" s="7" t="n"/>
+      <c r="L82" s="7" t="n"/>
+      <c r="M82" s="7" t="n"/>
+      <c r="N82" s="7" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>אלירן הפלינג</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="n"/>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>נתניה</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>053-7565565</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="n"/>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="n"/>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>אתה מפרסם בדפי זהב, משלם שיתקשרו. כמה שיחות נופלות כשאתה באמצע עבודה?</t>
+        </is>
+      </c>
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80383850/2550/</t>
+        </is>
+      </c>
+      <c r="K83" s="7" t="n"/>
+      <c r="L83" s="7" t="n"/>
+      <c r="M83" s="7" t="n"/>
+      <c r="N83" s="7" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>א.א. שירותי אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="n"/>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>נתניה</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>050-5399460</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="n"/>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>2 ביקורות, 4.1</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="n"/>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J84" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/21947020/2550/</t>
+        </is>
+      </c>
+      <c r="K84" s="7" t="n"/>
+      <c r="L84" s="7" t="n"/>
+      <c r="M84" s="7" t="n"/>
+      <c r="N84" s="7" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>רומן אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="n"/>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>נתניה</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>050-2685864</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="n"/>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>2 ביקורות, 5.0</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="n"/>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J85" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80173353/2550/</t>
+        </is>
+      </c>
+      <c r="K85" s="7" t="n"/>
+      <c r="L85" s="7" t="n"/>
+      <c r="M85" s="7" t="n"/>
+      <c r="N85" s="7" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>קבוצת האינסטלטורים</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="n"/>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>הרצליה</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>050-4401111</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="n"/>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>1 ביקורת, 3.8</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="n"/>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J86" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80255716/2550/</t>
+        </is>
+      </c>
+      <c r="K86" s="7" t="n"/>
+      <c r="L86" s="7" t="n"/>
+      <c r="M86" s="7" t="n"/>
+      <c r="N86" s="7" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>אסף האינסטלטור</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="n"/>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>פרדסיה</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>054-3012035</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="n"/>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>1 ביקורת, 5.0</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="n"/>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J87" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80214944/2550/</t>
+        </is>
+      </c>
+      <c r="K87" s="7" t="n"/>
+      <c r="L87" s="7" t="n"/>
+      <c r="M87" s="7" t="n"/>
+      <c r="N87" s="7" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>טיב - טק</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="n"/>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>נתניה</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>052-2781252</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="n"/>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>1 ביקורת, 5.0</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="n"/>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J88" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80091258/2550/</t>
+        </is>
+      </c>
+      <c r="K88" s="7" t="n"/>
+      <c r="L88" s="7" t="n"/>
+      <c r="M88" s="7" t="n"/>
+      <c r="N88" s="7" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>אייל - שרותי אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="n"/>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>הוד השרון</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>050-5295472</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="n"/>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>1 ביקורת, 4.6</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="n"/>
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t>כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J89" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/73732690/2550/</t>
+        </is>
+      </c>
+      <c r="K89" s="7" t="n"/>
+      <c r="L89" s="7" t="n"/>
+      <c r="M89" s="7" t="n"/>
+      <c r="N89" s="7" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>ע.ח מערכות מים</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="n"/>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>טבריה</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>054-6679912</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="n"/>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="n"/>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J90" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80388024/2550/</t>
+        </is>
+      </c>
+      <c r="K90" s="7" t="n"/>
+      <c r="L90" s="7" t="n"/>
+      <c r="M90" s="7" t="n"/>
+      <c r="N90" s="7" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>עלי אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="n"/>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>ערערה</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>050-6681463</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="n"/>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="n"/>
+      <c r="I91" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J91" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80393078/2550/</t>
+        </is>
+      </c>
+      <c r="K91" s="7" t="n"/>
+      <c r="L91" s="7" t="n"/>
+      <c r="M91" s="7" t="n"/>
+      <c r="N91" s="7" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>יאיר בניאס אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="n"/>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>עפולה</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>052-5181811</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="n"/>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="n"/>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>אתה מפרסם בדפי זהב, משלם שיתקשרו. כמה שיחות נופלות כשאתה באמצע עבודה?</t>
+        </is>
+      </c>
+      <c r="J92" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80376364/2550/</t>
+        </is>
+      </c>
+      <c r="K92" s="7" t="n"/>
+      <c r="L92" s="7" t="n"/>
+      <c r="M92" s="7" t="n"/>
+      <c r="N92" s="7" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>בני מרוואן נדאף אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="n"/>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>נצרת</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>052-6537884</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="n"/>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H93" s="4" t="n"/>
+      <c r="I93" s="4" t="inlineStr">
+        <is>
+          <t>אתה מפרסם בדפי זהב, משלם שיתקשרו. כמה שיחות נופלות כשאתה באמצע עבודה?</t>
+        </is>
+      </c>
+      <c r="J93" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80378634/2550/</t>
+        </is>
+      </c>
+      <c r="K93" s="7" t="n"/>
+      <c r="L93" s="7" t="n"/>
+      <c r="M93" s="7" t="n"/>
+      <c r="N93" s="7" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>ש. אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="n"/>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>פרדס חנה-כרכור</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>050-5602372</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="n"/>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="n"/>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>אתה מפרסם בדפי זהב, משלם שיתקשרו. כמה שיחות נופלות כשאתה באמצע עבודה?</t>
+        </is>
+      </c>
+      <c r="J94" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80387729/2550/</t>
+        </is>
+      </c>
+      <c r="K94" s="7" t="n"/>
+      <c r="L94" s="7" t="n"/>
+      <c r="M94" s="7" t="n"/>
+      <c r="N94" s="7" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>קובי תשובה עבודות אינסטלציה ואיתור נזילות</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="n"/>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>דלתון</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>050-8641444</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="n"/>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="n"/>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t>אתה מפרסם בדפי זהב, משלם שיתקשרו. כמה שיחות נופלות כשאתה באמצע עבודה?</t>
+        </is>
+      </c>
+      <c r="J95" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80264933/2550/</t>
+        </is>
+      </c>
+      <c r="K95" s="7" t="n"/>
+      <c r="L95" s="7" t="n"/>
+      <c r="M95" s="7" t="n"/>
+      <c r="N95" s="7" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>ג.ב עבודות אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="n"/>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>חדרה</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>052-5720331</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="n"/>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>2 ביקורות, 5.0</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="n"/>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J96" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80226389/2550/</t>
+        </is>
+      </c>
+      <c r="K96" s="7" t="n"/>
+      <c r="L96" s="7" t="n"/>
+      <c r="M96" s="7" t="n"/>
+      <c r="N96" s="7" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>מיסטר פלומבר אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="n"/>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>באר שבע</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>054-4400284</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="n"/>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H97" s="4" t="n"/>
+      <c r="I97" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J97" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80392432/2550/</t>
+        </is>
+      </c>
+      <c r="K97" s="7" t="n"/>
+      <c r="L97" s="7" t="n"/>
+      <c r="M97" s="7" t="n"/>
+      <c r="N97" s="7" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>אור אינסטלציה 24/7 אליאב תורג'מן</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="n"/>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>שדרות</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>054-5473086</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="n"/>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>3 ביקורות, 5.0</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="n"/>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J98" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80388259/2550/</t>
+        </is>
+      </c>
+      <c r="K98" s="7" t="n"/>
+      <c r="L98" s="7" t="n"/>
+      <c r="M98" s="7" t="n"/>
+      <c r="N98" s="7" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>ש.מ מערכות אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="n"/>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>באר שבע</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>052-3562138</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="n"/>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>3 ביקורות, 5.0</t>
+        </is>
+      </c>
+      <c r="H99" s="4" t="n"/>
+      <c r="I99" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J99" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80047672/2550/</t>
+        </is>
+      </c>
+      <c r="K99" s="7" t="n"/>
+      <c r="L99" s="7" t="n"/>
+      <c r="M99" s="7" t="n"/>
+      <c r="N99" s="7" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>מקסים פתרונות אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="n"/>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>באר שבע</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>054-5619165</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="n"/>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="n"/>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
+          <t>אתה מפרסם בדפי זהב, משלם שיתקשרו. כמה שיחות נופלות כשאתה באמצע עבודה?</t>
+        </is>
+      </c>
+      <c r="J100" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80390811/2550/</t>
+        </is>
+      </c>
+      <c r="K100" s="7" t="n"/>
+      <c r="L100" s="7" t="n"/>
+      <c r="M100" s="7" t="n"/>
+      <c r="N100" s="7" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>מאיר תיקונים ושיפוצים</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="n"/>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>שדרות</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>052-2885370</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="n"/>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H101" s="4" t="n"/>
+      <c r="I101" s="4" t="inlineStr">
+        <is>
+          <t>אתה מפרסם בדפי זהב, משלם שיתקשרו. כמה שיחות נופלות כשאתה באמצע עבודה?</t>
+        </is>
+      </c>
+      <c r="J101" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/28066440/2550/</t>
+        </is>
+      </c>
+      <c r="K101" s="7" t="n"/>
+      <c r="L101" s="7" t="n"/>
+      <c r="M101" s="7" t="n"/>
+      <c r="N101" s="7" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>ליאל פרויקטים</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="n"/>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>שדרות</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>054-6918141</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="n"/>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="n"/>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t>אתה מפרסם בדפי זהב, משלם שיתקשרו. כמה שיחות נופלות כשאתה באמצע עבודה?</t>
+        </is>
+      </c>
+      <c r="J102" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80355661/2550/</t>
+        </is>
+      </c>
+      <c r="K102" s="7" t="n"/>
+      <c r="L102" s="7" t="n"/>
+      <c r="M102" s="7" t="n"/>
+      <c r="N102" s="7" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>צוות מנצח-ביצוע עבודות שיפוצים</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="n"/>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>אילת</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>050-6057761</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="n"/>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H103" s="4" t="n"/>
+      <c r="I103" s="4" t="inlineStr">
+        <is>
+          <t>אתה מפרסם בדפי זהב, משלם שיתקשרו. כמה שיחות נופלות כשאתה באמצע עבודה?</t>
+        </is>
+      </c>
+      <c r="J103" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80386600/2550/</t>
+        </is>
+      </c>
+      <c r="K103" s="7" t="n"/>
+      <c r="L103" s="7" t="n"/>
+      <c r="M103" s="7" t="n"/>
+      <c r="N103" s="7" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>אליאב אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="n"/>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>אופקים</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>054-6901549</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="n"/>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>1 ביקורת, 5.0</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="n"/>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J104" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80165525/2550/</t>
+        </is>
+      </c>
+      <c r="K104" s="7" t="n"/>
+      <c r="L104" s="7" t="n"/>
+      <c r="M104" s="7" t="n"/>
+      <c r="N104" s="7" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>אמנו אינסטלטור צדיק</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="n"/>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>אשקלון</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>052-8484855</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="n"/>
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t>2 ביקורות, 5.0</t>
+        </is>
+      </c>
+      <c r="H105" s="4" t="n"/>
+      <c r="I105" s="4" t="inlineStr">
+        <is>
+          <t>כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J105" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80152882/2550/</t>
+        </is>
+      </c>
+      <c r="K105" s="7" t="n"/>
+      <c r="L105" s="7" t="n"/>
+      <c r="M105" s="7" t="n"/>
+      <c r="N105" s="7" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>מגוז יוסף</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="n"/>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>אשקלון</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>052-2711114</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="n"/>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>1 ביקורת, 5.0</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="n"/>
+      <c r="I106" s="4" t="inlineStr">
+        <is>
+          <t>כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J106" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/14902750/2550/</t>
+        </is>
+      </c>
+      <c r="K106" s="7" t="n"/>
+      <c r="L106" s="7" t="n"/>
+      <c r="M106" s="7" t="n"/>
+      <c r="N106" s="7" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>בוכריס אינסטלטור</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="n"/>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>אשקלון</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>054-2019118</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="n"/>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>1 ביקורת, 5.0</t>
+        </is>
+      </c>
+      <c r="H107" s="4" t="n"/>
+      <c r="I107" s="4" t="inlineStr">
+        <is>
+          <t>כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J107" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80350352/2550/</t>
+        </is>
+      </c>
+      <c r="K107" s="7" t="n"/>
+      <c r="L107" s="7" t="n"/>
+      <c r="M107" s="7" t="n"/>
+      <c r="N107" s="7" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>חיים מנחם</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="n"/>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>נחושה</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>052-2539513</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="n"/>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t>1 ביקורת, 4.6</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="n"/>
+      <c r="I108" s="4" t="inlineStr">
+        <is>
+          <t>כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J108" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/40014260/2550/</t>
+        </is>
+      </c>
+      <c r="K108" s="7" t="n"/>
+      <c r="L108" s="7" t="n"/>
+      <c r="M108" s="7" t="n"/>
+      <c r="N108" s="7" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>שלום דערי- שירותי אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="n"/>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>נס ציונה</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>053-5574729</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="n"/>
+      <c r="G109" s="4" t="inlineStr">
+        <is>
+          <t>4 ביקורות, 4.4</t>
+        </is>
+      </c>
+      <c r="H109" s="4" t="n"/>
+      <c r="I109" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J109" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/33464420/2550/</t>
+        </is>
+      </c>
+      <c r="K109" s="7" t="n"/>
+      <c r="L109" s="7" t="n"/>
+      <c r="M109" s="7" t="n"/>
+      <c r="N109" s="7" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>עומר אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="n"/>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>יבנה</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>054-5812366</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="n"/>
+      <c r="G110" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="n"/>
+      <c r="I110" s="4" t="inlineStr">
+        <is>
+          <t>אתה מפרסם בדפי זהב, משלם שיתקשרו. כמה שיחות נופלות כשאתה באמצע עבודה?</t>
+        </is>
+      </c>
+      <c r="J110" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80367222/2550/</t>
+        </is>
+      </c>
+      <c r="K110" s="7" t="n"/>
+      <c r="L110" s="7" t="n"/>
+      <c r="M110" s="7" t="n"/>
+      <c r="N110" s="7" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>מוניטין פרויקטים</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="n"/>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>יבנה</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>053-7519645</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="n"/>
+      <c r="G111" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H111" s="4" t="n"/>
+      <c r="I111" s="4" t="inlineStr">
+        <is>
+          <t>אתה מפרסם בדפי זהב, משלם שיתקשרו. כמה שיחות נופלות כשאתה באמצע עבודה?</t>
+        </is>
+      </c>
+      <c r="J111" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/28044090/2550/</t>
+        </is>
+      </c>
+      <c r="K111" s="7" t="n"/>
+      <c r="L111" s="7" t="n"/>
+      <c r="M111" s="7" t="n"/>
+      <c r="N111" s="7" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>שירותי אינסטלציה מקצועיים ברחובות - עוז שיפוצים ואחזקות</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="n"/>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>רחובות</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>052-7988150</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="n"/>
+      <c r="G112" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="n"/>
+      <c r="I112" s="4" t="inlineStr">
+        <is>
+          <t>אתה מפרסם בדפי זהב, משלם שיתקשרו. כמה שיחות נופלות כשאתה באמצע עבודה?</t>
+        </is>
+      </c>
+      <c r="J112" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80360432/2550/</t>
+        </is>
+      </c>
+      <c r="K112" s="7" t="n"/>
+      <c r="L112" s="7" t="n"/>
+      <c r="M112" s="7" t="n"/>
+      <c r="N112" s="7" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>יורי אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="n"/>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>בני עי"ש</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>058-4260576</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="n"/>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H113" s="4" t="n"/>
+      <c r="I113" s="4" t="inlineStr">
+        <is>
+          <t>אתה מפרסם בדפי זהב, משלם שיתקשרו. כמה שיחות נופלות כשאתה באמצע עבודה?</t>
+        </is>
+      </c>
+      <c r="J113" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80392325/2550/</t>
+        </is>
+      </c>
+      <c r="K113" s="7" t="n"/>
+      <c r="L113" s="7" t="n"/>
+      <c r="M113" s="7" t="n"/>
+      <c r="N113" s="7" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>איציק אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="n"/>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>גן יבנה</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>052-2645692</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="n"/>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
+          <t>4 ביקורות, 4.4</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="n"/>
+      <c r="I114" s="4" t="inlineStr">
+        <is>
+          <t>כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J114" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/25321580/2550/</t>
+        </is>
+      </c>
+      <c r="K114" s="7" t="n"/>
+      <c r="L114" s="7" t="n"/>
+      <c r="M114" s="7" t="n"/>
+      <c r="N114" s="7" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>מנחם קלימיאן אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="n"/>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>קרית מלאכי</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>055-6626840</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="n"/>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>1 ביקורת, 5.0</t>
+        </is>
+      </c>
+      <c r="H115" s="4" t="n"/>
+      <c r="I115" s="4" t="inlineStr">
+        <is>
+          <t>כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J115" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80378890/2550/</t>
+        </is>
+      </c>
+      <c r="K115" s="7" t="n"/>
+      <c r="L115" s="7" t="n"/>
+      <c r="M115" s="7" t="n"/>
+      <c r="N115" s="7" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>איציק אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="n"/>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>ירושלים</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>050-5298171</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="n"/>
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="n"/>
+      <c r="I116" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J116" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80372803/2550/</t>
+        </is>
+      </c>
+      <c r="K116" s="7" t="n"/>
+      <c r="L116" s="7" t="n"/>
+      <c r="M116" s="7" t="n"/>
+      <c r="N116" s="7" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>קימו קיד אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="n"/>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>ירושלים</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>053-3900156</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="n"/>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H117" s="4" t="n"/>
+      <c r="I117" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J117" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80393362/2550/</t>
+        </is>
+      </c>
+      <c r="K117" s="7" t="n"/>
+      <c r="L117" s="7" t="n"/>
+      <c r="M117" s="7" t="n"/>
+      <c r="N117" s="7" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>לינדנבאום יוסף</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="n"/>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>ירושלים</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>054-7280989</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="n"/>
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t>1 ביקורת, 5.0</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="n"/>
+      <c r="I118" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J118" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/67902240/2550/</t>
+        </is>
+      </c>
+      <c r="K118" s="7" t="n"/>
+      <c r="L118" s="7" t="n"/>
+      <c r="M118" s="7" t="n"/>
+      <c r="N118" s="7" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>אשר שירותי אינסטלציה 24 ש'</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="n"/>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>ירושלים</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>052-5667771</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="n"/>
+      <c r="G119" s="4" t="inlineStr">
+        <is>
+          <t>2 ביקורות, 4.0</t>
+        </is>
+      </c>
+      <c r="H119" s="4" t="n"/>
+      <c r="I119" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J119" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80134535/2550/</t>
+        </is>
+      </c>
+      <c r="K119" s="7" t="n"/>
+      <c r="L119" s="7" t="n"/>
+      <c r="M119" s="7" t="n"/>
+      <c r="N119" s="7" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>שחר אלון כל עבודות האינסטלציה</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="n"/>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>בית שמש</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>054-4752389</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="n"/>
+      <c r="G120" s="4" t="inlineStr">
+        <is>
+          <t>1 ביקורת, 4.4</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="n"/>
+      <c r="I120" s="4" t="inlineStr">
+        <is>
+          <t>כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J120" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80141916/2550/</t>
+        </is>
+      </c>
+      <c r="K120" s="7" t="n"/>
+      <c r="L120" s="7" t="n"/>
+      <c r="M120" s="7" t="n"/>
+      <c r="N120" s="7" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>ב</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>שרברבות 2010</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="n"/>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>אבן ספיר</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>053-7379115</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="n"/>
+      <c r="G121" s="4" t="inlineStr">
+        <is>
+          <t>1 ביקורת, 4.0</t>
+        </is>
+      </c>
+      <c r="H121" s="4" t="n"/>
+      <c r="I121" s="4" t="inlineStr">
+        <is>
+          <t>כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J121" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80055537/2550/</t>
+        </is>
+      </c>
+      <c r="K121" s="7" t="n"/>
+      <c r="L121" s="7" t="n"/>
+      <c r="M121" s="7" t="n"/>
+      <c r="N121" s="7" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>ג</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>בועז פלד - אינסטלטור מנוסה</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="n"/>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>ראש העין</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>054-4643933</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="n"/>
+      <c r="G122" s="4" t="inlineStr">
+        <is>
+          <t>5 ביקורות, 2.7</t>
+        </is>
+      </c>
+      <c r="H122" s="4" t="n"/>
+      <c r="I122" s="4" t="inlineStr">
+        <is>
+          <t>אתה מפרסם בדפי זהב, משלם שיתקשרו. כמה שיחות נופלות כשאתה באמצע עבודה?</t>
+        </is>
+      </c>
+      <c r="J122" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80362532/2550/</t>
+        </is>
+      </c>
+      <c r="K122" s="7" t="n"/>
+      <c r="L122" s="7" t="n"/>
+      <c r="M122" s="7" t="n"/>
+      <c r="N122" s="7" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>ג</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>י.ל. אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="n"/>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>בת ים</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>054-3244164</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="n"/>
+      <c r="G123" s="4" t="inlineStr">
+        <is>
+          <t>1 ביקורת, 2.6</t>
+        </is>
+      </c>
+      <c r="H123" s="4" t="n"/>
+      <c r="I123" s="4" t="inlineStr">
+        <is>
+          <t>כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J123" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80110591/2550/</t>
+        </is>
+      </c>
+      <c r="K123" s="7" t="n"/>
+      <c r="L123" s="7" t="n"/>
+      <c r="M123" s="7" t="n"/>
+      <c r="N123" s="7" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>ג</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>MARIO מריו</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="n"/>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>ראשון לציון</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>050-6579218</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="n"/>
+      <c r="G124" s="4" t="inlineStr">
+        <is>
+          <t>1 ביקורת, 1.5</t>
+        </is>
+      </c>
+      <c r="H124" s="4" t="n"/>
+      <c r="I124" s="4" t="inlineStr">
+        <is>
+          <t>כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J124" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80294901/2550/</t>
+        </is>
+      </c>
+      <c r="K124" s="7" t="n"/>
+      <c r="L124" s="7" t="n"/>
+      <c r="M124" s="7" t="n"/>
+      <c r="N124" s="7" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>ג</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>מוקד משאבות</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="n"/>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>תל אביב</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>052-6482377</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="n"/>
+      <c r="G125" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H125" s="4" t="n"/>
+      <c r="I125" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J125" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80180902/2550/</t>
+        </is>
+      </c>
+      <c r="K125" s="7" t="n"/>
+      <c r="L125" s="7" t="n"/>
+      <c r="M125" s="7" t="n"/>
+      <c r="N125" s="7" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>ג</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>ג'ייקוב פיצחדזה</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="n"/>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>תל אביב</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>050-4810417</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="n"/>
+      <c r="G126" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H126" s="4" t="n"/>
+      <c r="I126" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J126" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80356559/2550/</t>
+        </is>
+      </c>
+      <c r="K126" s="7" t="n"/>
+      <c r="L126" s="7" t="n"/>
+      <c r="M126" s="7" t="n"/>
+      <c r="N126" s="7" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>ג</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>ליעוז</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="n"/>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>אור יהודה</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>050-2775456</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="n"/>
+      <c r="G127" s="4" t="inlineStr">
+        <is>
+          <t>1 ביקורת, 1.0</t>
+        </is>
+      </c>
+      <c r="H127" s="4" t="n"/>
+      <c r="I127" s="4" t="inlineStr">
+        <is>
+          <t>כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J127" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80192286/2550/</t>
+        </is>
+      </c>
+      <c r="K127" s="7" t="n"/>
+      <c r="L127" s="7" t="n"/>
+      <c r="M127" s="7" t="n"/>
+      <c r="N127" s="7" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>ג</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>א.אדיר שרותי אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="n"/>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>יהוד-מונוסון</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>054-3001004</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="n"/>
+      <c r="G128" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H128" s="4" t="n"/>
+      <c r="I128" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J128" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80060866/2550/</t>
+        </is>
+      </c>
+      <c r="K128" s="7" t="n"/>
+      <c r="L128" s="7" t="n"/>
+      <c r="M128" s="7" t="n"/>
+      <c r="N128" s="7" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>ג</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>אמינות השיפוצים</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="n"/>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>חולון</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>050-5616166</t>
+        </is>
+      </c>
+      <c r="F129" s="4" t="n"/>
+      <c r="G129" s="4" t="inlineStr">
+        <is>
+          <t>1 ביקורת, 1.0</t>
+        </is>
+      </c>
+      <c r="H129" s="4" t="n"/>
+      <c r="I129" s="4" t="inlineStr">
+        <is>
+          <t>כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J129" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80018279/2550/</t>
+        </is>
+      </c>
+      <c r="K129" s="7" t="n"/>
+      <c r="L129" s="7" t="n"/>
+      <c r="M129" s="7" t="n"/>
+      <c r="N129" s="7" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>ג</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>מיקיטס אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="n"/>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
+          <t>תל אביב</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="inlineStr">
+        <is>
+          <t>052-4590178</t>
+        </is>
+      </c>
+      <c r="F130" s="4" t="n"/>
+      <c r="G130" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H130" s="4" t="n"/>
+      <c r="I130" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J130" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80041508/2550/</t>
+        </is>
+      </c>
+      <c r="K130" s="7" t="n"/>
+      <c r="L130" s="7" t="n"/>
+      <c r="M130" s="7" t="n"/>
+      <c r="N130" s="7" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>ג</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>יס אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="n"/>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>תל אביב</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>055-9955116</t>
+        </is>
+      </c>
+      <c r="F131" s="4" t="n"/>
+      <c r="G131" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H131" s="4" t="n"/>
+      <c r="I131" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J131" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80315968/2550/</t>
+        </is>
+      </c>
+      <c r="K131" s="7" t="n"/>
+      <c r="L131" s="7" t="n"/>
+      <c r="M131" s="7" t="n"/>
+      <c r="N131" s="7" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>ג</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>א.ר.י. אינסטלציה ואחזקת מבנים</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="n"/>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
+          <t>תל אביב</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>052-5008468</t>
+        </is>
+      </c>
+      <c r="F132" s="4" t="n"/>
+      <c r="G132" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H132" s="4" t="n"/>
+      <c r="I132" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J132" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80110951/2550/</t>
+        </is>
+      </c>
+      <c r="K132" s="7" t="n"/>
+      <c r="L132" s="7" t="n"/>
+      <c r="M132" s="7" t="n"/>
+      <c r="N132" s="7" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>ג</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>אינסטלציה יעוץ וביצוע</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="n"/>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>תל אביב</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>053-3327045</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="n"/>
+      <c r="G133" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H133" s="4" t="n"/>
+      <c r="I133" s="4" t="inlineStr">
+        <is>
+          <t>כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J133" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80343579/2550/</t>
+        </is>
+      </c>
+      <c r="K133" s="7" t="n"/>
+      <c r="L133" s="7" t="n"/>
+      <c r="M133" s="7" t="n"/>
+      <c r="N133" s="7" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>ג</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>גבריאל האינסטלטור</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="n"/>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>ראשון לציון</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>052-7747202</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="n"/>
+      <c r="G134" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H134" s="4" t="n"/>
+      <c r="I134" s="4" t="inlineStr">
+        <is>
+          <t>כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J134" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80119738/2550/</t>
+        </is>
+      </c>
+      <c r="K134" s="7" t="n"/>
+      <c r="L134" s="7" t="n"/>
+      <c r="M134" s="7" t="n"/>
+      <c r="N134" s="7" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>ג</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>אינסטלטור הגיסים</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="n"/>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>תל אביב</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>052-3768606</t>
+        </is>
+      </c>
+      <c r="F135" s="4" t="n"/>
+      <c r="G135" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H135" s="4" t="n"/>
+      <c r="I135" s="4" t="inlineStr">
+        <is>
+          <t>כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J135" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80076885/2550/</t>
+        </is>
+      </c>
+      <c r="K135" s="7" t="n"/>
+      <c r="L135" s="7" t="n"/>
+      <c r="M135" s="7" t="n"/>
+      <c r="N135" s="7" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t>ג</t>
+        </is>
+      </c>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>אינסטלטור אורי</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="n"/>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t>אזור</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>050-8634455</t>
+        </is>
+      </c>
+      <c r="F136" s="4" t="n"/>
+      <c r="G136" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H136" s="4" t="n"/>
+      <c r="I136" s="4" t="inlineStr">
+        <is>
+          <t>כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J136" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80206662/2550/</t>
+        </is>
+      </c>
+      <c r="K136" s="7" t="n"/>
+      <c r="L136" s="7" t="n"/>
+      <c r="M136" s="7" t="n"/>
+      <c r="N136" s="7" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>ג</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>האינסטלטור הגיבור</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="n"/>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>גבעתיים</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="inlineStr">
+        <is>
+          <t>054-4898903</t>
+        </is>
+      </c>
+      <c r="F137" s="4" t="n"/>
+      <c r="G137" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H137" s="4" t="n"/>
+      <c r="I137" s="4" t="inlineStr">
+        <is>
+          <t>כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J137" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80374561/2550/</t>
+        </is>
+      </c>
+      <c r="K137" s="7" t="n"/>
+      <c r="L137" s="7" t="n"/>
+      <c r="M137" s="7" t="n"/>
+      <c r="N137" s="7" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>ג</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>נ.ס אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="n"/>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>תל אביב</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="inlineStr">
+        <is>
+          <t>054-2333595</t>
+        </is>
+      </c>
+      <c r="F138" s="4" t="n"/>
+      <c r="G138" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H138" s="4" t="n"/>
+      <c r="I138" s="4" t="inlineStr">
+        <is>
+          <t>כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J138" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80359267/2550/</t>
+        </is>
+      </c>
+      <c r="K138" s="7" t="n"/>
+      <c r="L138" s="7" t="n"/>
+      <c r="M138" s="7" t="n"/>
+      <c r="N138" s="7" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>ג</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>איתורי נזילות צנרת-אדיב</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="n"/>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>רעננה</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="inlineStr">
+        <is>
+          <t>050-3080080</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="n"/>
+      <c r="G139" s="4" t="inlineStr">
+        <is>
+          <t>1 ביקורת, 1.0</t>
+        </is>
+      </c>
+      <c r="H139" s="4" t="n"/>
+      <c r="I139" s="4" t="inlineStr">
+        <is>
+          <t>אתה מפרסם בדפי זהב, משלם שיתקשרו. כמה שיחות נופלות כשאתה באמצע עבודה?</t>
+        </is>
+      </c>
+      <c r="J139" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80053961/2550/</t>
+        </is>
+      </c>
+      <c r="K139" s="7" t="n"/>
+      <c r="L139" s="7" t="n"/>
+      <c r="M139" s="7" t="n"/>
+      <c r="N139" s="7" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>ג</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>אריק אינסטלציה ותיקונים</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="n"/>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>רמות השבים</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="inlineStr">
+        <is>
+          <t>052-4583897</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="n"/>
+      <c r="G140" s="4" t="inlineStr">
+        <is>
+          <t>1 ביקורת, 1.0</t>
+        </is>
+      </c>
+      <c r="H140" s="4" t="n"/>
+      <c r="I140" s="4" t="inlineStr">
+        <is>
+          <t>כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J140" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/76014530/2550/</t>
+        </is>
+      </c>
+      <c r="K140" s="7" t="n"/>
+      <c r="L140" s="7" t="n"/>
+      <c r="M140" s="7" t="n"/>
+      <c r="N140" s="7" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>ג</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>אורן גרעיני</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="n"/>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>כפר יונה</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="inlineStr">
+        <is>
+          <t>050-8838162</t>
+        </is>
+      </c>
+      <c r="F141" s="4" t="n"/>
+      <c r="G141" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H141" s="4" t="n"/>
+      <c r="I141" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J141" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80101106/2550/</t>
+        </is>
+      </c>
+      <c r="K141" s="7" t="n"/>
+      <c r="L141" s="7" t="n"/>
+      <c r="M141" s="7" t="n"/>
+      <c r="N141" s="7" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>ג</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>אינסטלטור מוסמך איל גלעד</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="n"/>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>הרצליה</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="inlineStr">
+        <is>
+          <t>052-2534455</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="n"/>
+      <c r="G142" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H142" s="4" t="n"/>
+      <c r="I142" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J142" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/31953770/2550/</t>
+        </is>
+      </c>
+      <c r="K142" s="7" t="n"/>
+      <c r="L142" s="7" t="n"/>
+      <c r="M142" s="7" t="n"/>
+      <c r="N142" s="7" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>ג</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>יגאל גולני</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="n"/>
+      <c r="D143" s="4" t="inlineStr">
+        <is>
+          <t>צור יגאל</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="inlineStr">
+        <is>
+          <t>050-7440000</t>
+        </is>
+      </c>
+      <c r="F143" s="4" t="n"/>
+      <c r="G143" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H143" s="4" t="n"/>
+      <c r="I143" s="4" t="inlineStr">
+        <is>
+          <t>כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J143" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80047540/2550/</t>
+        </is>
+      </c>
+      <c r="K143" s="7" t="n"/>
+      <c r="L143" s="7" t="n"/>
+      <c r="M143" s="7" t="n"/>
+      <c r="N143" s="7" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t>ג</t>
+        </is>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>שירותי תיקונים</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="n"/>
+      <c r="D144" s="4" t="inlineStr">
+        <is>
+          <t>הרצליה</t>
+        </is>
+      </c>
+      <c r="E144" s="5" t="inlineStr">
+        <is>
+          <t>052-2503750</t>
+        </is>
+      </c>
+      <c r="F144" s="4" t="n"/>
+      <c r="G144" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H144" s="4" t="n"/>
+      <c r="I144" s="4" t="inlineStr">
+        <is>
+          <t>כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J144" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80355628/2550/</t>
+        </is>
+      </c>
+      <c r="K144" s="7" t="n"/>
+      <c r="L144" s="7" t="n"/>
+      <c r="M144" s="7" t="n"/>
+      <c r="N144" s="7" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>ג</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>יוסף אליהו אינסטלטור</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="n"/>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>נתניה</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="inlineStr">
+        <is>
+          <t>053-5225770</t>
+        </is>
+      </c>
+      <c r="F145" s="4" t="n"/>
+      <c r="G145" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H145" s="4" t="n"/>
+      <c r="I145" s="4" t="inlineStr">
+        <is>
+          <t>כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J145" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80279177/2550/</t>
+        </is>
+      </c>
+      <c r="K145" s="7" t="n"/>
+      <c r="L145" s="7" t="n"/>
+      <c r="M145" s="7" t="n"/>
+      <c r="N145" s="7" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="inlineStr">
+        <is>
+          <t>ג</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="inlineStr">
+        <is>
+          <t>שמעון בן-ברית מקצוען ולעניין</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="n"/>
+      <c r="D146" s="4" t="inlineStr">
+        <is>
+          <t>חיבת ציון</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="inlineStr">
+        <is>
+          <t>052-2417647</t>
+        </is>
+      </c>
+      <c r="F146" s="4" t="n"/>
+      <c r="G146" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H146" s="4" t="n"/>
+      <c r="I146" s="4" t="inlineStr">
+        <is>
+          <t>כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J146" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/16065320/2550/</t>
+        </is>
+      </c>
+      <c r="K146" s="7" t="n"/>
+      <c r="L146" s="7" t="n"/>
+      <c r="M146" s="7" t="n"/>
+      <c r="N146" s="7" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>ג</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>סהר אינסטלציה ושיפוצים</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="n"/>
+      <c r="D147" s="4" t="inlineStr">
+        <is>
+          <t>נתניה</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="inlineStr">
+        <is>
+          <t>052-5599391</t>
+        </is>
+      </c>
+      <c r="F147" s="4" t="n"/>
+      <c r="G147" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H147" s="4" t="n"/>
+      <c r="I147" s="4" t="inlineStr">
+        <is>
+          <t>כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J147" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/38120540/2550/</t>
+        </is>
+      </c>
+      <c r="K147" s="7" t="n"/>
+      <c r="L147" s="7" t="n"/>
+      <c r="M147" s="7" t="n"/>
+      <c r="N147" s="7" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="inlineStr">
+        <is>
+          <t>ג</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>יגאל שיפוצים</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="n"/>
+      <c r="D148" s="4" t="inlineStr">
+        <is>
+          <t>באר שבע</t>
+        </is>
+      </c>
+      <c r="E148" s="5" t="inlineStr">
+        <is>
+          <t>050-6862673</t>
+        </is>
+      </c>
+      <c r="F148" s="4" t="n"/>
+      <c r="G148" s="4" t="inlineStr">
+        <is>
+          <t>4 ביקורות, 2.9</t>
+        </is>
+      </c>
+      <c r="H148" s="4" t="n"/>
+      <c r="I148" s="4" t="inlineStr">
+        <is>
+          <t>כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J148" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80119672/2550/</t>
+        </is>
+      </c>
+      <c r="K148" s="7" t="n"/>
+      <c r="L148" s="7" t="n"/>
+      <c r="M148" s="7" t="n"/>
+      <c r="N148" s="7" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>ג</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>עדי לוי - האינסטלטור המוביל במודיעין</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="n"/>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t>מודיעין-מכבים-רעות</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="inlineStr">
+        <is>
+          <t>054-9939577</t>
+        </is>
+      </c>
+      <c r="F149" s="4" t="n"/>
+      <c r="G149" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H149" s="4" t="n"/>
+      <c r="I149" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J149" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80363294/2550/</t>
+        </is>
+      </c>
+      <c r="K149" s="7" t="n"/>
+      <c r="L149" s="7" t="n"/>
+      <c r="M149" s="7" t="n"/>
+      <c r="N149" s="7" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t>ג</t>
+        </is>
+      </c>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
+          <t>אלי האינסטלטור שלכם</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="n"/>
+      <c r="D150" s="4" t="inlineStr">
+        <is>
+          <t>נס ציונה</t>
+        </is>
+      </c>
+      <c r="E150" s="5" t="inlineStr">
+        <is>
+          <t>050-5330442</t>
+        </is>
+      </c>
+      <c r="F150" s="4" t="n"/>
+      <c r="G150" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H150" s="4" t="n"/>
+      <c r="I150" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J150" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/18049390/2550/</t>
+        </is>
+      </c>
+      <c r="K150" s="7" t="n"/>
+      <c r="L150" s="7" t="n"/>
+      <c r="M150" s="7" t="n"/>
+      <c r="N150" s="7" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>ג</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>האינסטלטור של מודיעין והסביבה</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="n"/>
+      <c r="D151" s="4" t="inlineStr">
+        <is>
+          <t>מודיעין-מכבים-רעות</t>
+        </is>
+      </c>
+      <c r="E151" s="5" t="inlineStr">
+        <is>
+          <t>054-4620412</t>
+        </is>
+      </c>
+      <c r="F151" s="4" t="n"/>
+      <c r="G151" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H151" s="4" t="n"/>
+      <c r="I151" s="4" t="inlineStr">
+        <is>
+          <t>אתה עובד 24 שעות. בשתיים בלילה, או כשהידיים בצנרת, מי עונה ללקוח?</t>
+        </is>
+      </c>
+      <c r="J151" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/36824400/2550/</t>
+        </is>
+      </c>
+      <c r="K151" s="7" t="n"/>
+      <c r="L151" s="7" t="n"/>
+      <c r="M151" s="7" t="n"/>
+      <c r="N151" s="7" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="4" t="inlineStr">
+        <is>
+          <t>ג</t>
+        </is>
+      </c>
+      <c r="B152" s="4" t="inlineStr">
+        <is>
+          <t>מערכות מים</t>
+        </is>
+      </c>
+      <c r="C152" s="4" t="n"/>
+      <c r="D152" s="4" t="inlineStr">
+        <is>
+          <t>רמלה</t>
+        </is>
+      </c>
+      <c r="E152" s="5" t="inlineStr">
+        <is>
+          <t>054-3035391</t>
+        </is>
+      </c>
+      <c r="F152" s="4" t="n"/>
+      <c r="G152" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H152" s="4" t="n"/>
+      <c r="I152" s="4" t="inlineStr">
+        <is>
+          <t>כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J152" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80162465/2550/</t>
+        </is>
+      </c>
+      <c r="K152" s="7" t="n"/>
+      <c r="L152" s="7" t="n"/>
+      <c r="M152" s="7" t="n"/>
+      <c r="N152" s="7" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>ג</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>זורמים אנסטלציה ותשתיות מים</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="n"/>
+      <c r="D153" s="4" t="inlineStr">
+        <is>
+          <t>בית שמש</t>
+        </is>
+      </c>
+      <c r="E153" s="5" t="inlineStr">
+        <is>
+          <t>054-7684468</t>
+        </is>
+      </c>
+      <c r="F153" s="4" t="n"/>
+      <c r="G153" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H153" s="4" t="n"/>
+      <c r="I153" s="4" t="inlineStr">
+        <is>
+          <t>כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J153" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80136851/2550/</t>
+        </is>
+      </c>
+      <c r="K153" s="7" t="n"/>
+      <c r="L153" s="7" t="n"/>
+      <c r="M153" s="7" t="n"/>
+      <c r="N153" s="7" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t>ג</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>נתנאל אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="n"/>
+      <c r="D154" s="4" t="inlineStr">
+        <is>
+          <t>ירושלים</t>
+        </is>
+      </c>
+      <c r="E154" s="5" t="inlineStr">
+        <is>
+          <t>054-4941884</t>
+        </is>
+      </c>
+      <c r="F154" s="4" t="n"/>
+      <c r="G154" s="4" t="inlineStr">
+        <is>
+          <t>אין ביקורות</t>
+        </is>
+      </c>
+      <c r="H154" s="4" t="n"/>
+      <c r="I154" s="4" t="inlineStr">
+        <is>
+          <t>כשאתה באמצע עבודה ומתקשרים, מה קורה עם השיחה?</t>
+        </is>
+      </c>
+      <c r="J154" s="6" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/40989350/2550/</t>
+        </is>
+      </c>
+      <c r="K154" s="7" t="n"/>
+      <c r="L154" s="7" t="n"/>
+      <c r="M154" s="7" t="n"/>
+      <c r="N154" s="7" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
         <is>
           <t>הערות:</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" t="inlineStr">
         <is>
           <t>א = בעל עסק עם נייד וביקורות. מתחילים מהם. ב = פחות ביקורות, או אולי עסק גדול (אופק).</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" t="inlineStr">
         <is>
           <t>עמרם ואלכס אולי צוות קטן ולא אדם אחד. אצלם שואלים מי עונה לטלפון כשכולם בשטח.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" t="inlineStr">
         <is>
           <t>אביר, אדיר, יהודה, יניב לא עובדים 24/7. אצלם מדברים על פניות בערב ובשבת.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" t="inlineStr">
         <is>
           <t>איש קשר שנלקח רק משם העסק עלול להיות לא נכון. בפתיחה שואלים: "מדבר עם בעל העסק?"</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>הדירוגים מדפי זהב (d.co.il), נבדקו ב-15/10/2026.</t>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>הדירוגים מדפי זהב (d.co.il): 1-20 נבדקו ב-15/10/2026, 21-150 ב-21/10/2026. עדיפות ג = בלי ביקורות או דירוג נמוך, מתקשרים אליהם אחרונים.</t>
         </is>
       </c>
     </row>
@@ -1715,28 +7435,6 @@
       <formula1>"לא ענה,לחזור אליו,שלחתי דמו,נקבעה שיחה,סגרנו,לא מעוניין,לא מתאים"</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId20"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>